--- a/inst/extdata/LC_columns.xlsx
+++ b/inst/extdata/LC_columns.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\home\aRmel_package\proteoCraft\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C4C644-76FC-4004-B877-0885D41EE7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE18B3FE-EDE6-447D-A764-ACCF27652239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="131">
   <si>
     <t>Name</t>
   </si>
@@ -424,6 +424,9 @@
   </si>
   <si>
     <t>PepSep</t>
+  </si>
+  <si>
+    <t>Acquity Premier BEH C18</t>
   </si>
 </sst>
 </file>
@@ -1390,8 +1393,8 @@
       <c r="D17" s="4">
         <v>10</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>60</v>
+      <c r="E17" s="4">
+        <v>2100</v>
       </c>
       <c r="F17" s="7">
         <v>2.7</v>
@@ -1417,7 +1420,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>130</v>
       </c>
       <c r="B18" t="s">
         <v>87</v>
@@ -1428,7 +1431,7 @@
       <c r="D18" s="4">
         <v>5</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="4">
         <v>2100</v>
       </c>
       <c r="F18" s="7" t="s">
@@ -1828,7 +1831,9 @@
       <c r="F29" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G29" s="7"/>
+      <c r="G29" s="7" t="s">
+        <v>105</v>
+      </c>
       <c r="H29" t="s">
         <v>14</v>
       </c>
@@ -1864,7 +1869,9 @@
       <c r="F30" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G30" s="7"/>
+      <c r="G30" s="7" t="s">
+        <v>105</v>
+      </c>
       <c r="H30" t="s">
         <v>14</v>
       </c>
